--- a/data/clientes.xlsx
+++ b/data/clientes.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bancolombia-my.sharepoint.com/personal/mteran_bancolombia_com_co/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jomaver/Library/CloudStorage/OneDrive-GrupoBancolombia/Otros/Trend_Digest/Riesgos/News-Scrapper/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47EC5109-66D6-4332-BEA8-846ED0E2917B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B8555C-8108-D948-B12C-220800DB472A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28690" yWindow="-110" windowWidth="29020" windowHeight="15820" xr2:uid="{B4160771-E885-4268-9E3B-923D2C6334DB}"/>
+    <workbookView xWindow="5540" yWindow="760" windowWidth="29020" windowHeight="15820" activeTab="1" xr2:uid="{B4160771-E885-4268-9E3B-923D2C6334DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Excludes" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_CH">110000</definedName>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Emisor</t>
   </si>
@@ -166,6 +167,12 @@
   </si>
   <si>
     <t>ENEL</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>peru21.pe</t>
   </si>
 </sst>
 </file>
@@ -578,11 +585,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B14AF44F-A1D1-414E-897F-ECD542EC8E25}">
   <dimension ref="A1:A34"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="42.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="10.85546875" style="1"/>
+    <col min="1" max="1" width="42.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -758,4 +765,24 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EE42B21-E03D-7A4B-8A50-D148BE395929}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/clientes.xlsx
+++ b/data/clientes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jomaver/Library/CloudStorage/OneDrive-GrupoBancolombia/Otros/Trend_Digest/Riesgos/News-Scrapper/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B8555C-8108-D948-B12C-220800DB472A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86461C54-4E69-6645-90A4-036A889ED3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5540" yWindow="760" windowWidth="29020" windowHeight="15820" activeTab="1" xr2:uid="{B4160771-E885-4268-9E3B-923D2C6334DB}"/>
+    <workbookView xWindow="5540" yWindow="760" windowWidth="29020" windowHeight="15820" xr2:uid="{B4160771-E885-4268-9E3B-923D2C6334DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Emisor</t>
   </si>
@@ -173,6 +173,9 @@
   </si>
   <si>
     <t>peru21.pe</t>
+  </si>
+  <si>
+    <t>Lenguaje</t>
   </si>
 </sst>
 </file>
@@ -584,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B14AF44F-A1D1-414E-897F-ECD542EC8E25}">
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="42.1640625" style="1" customWidth="1"/>
@@ -592,82 +595,85 @@
     <col min="3" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="B1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:2">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:2">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:2">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:2">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:2">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>

--- a/data/clientes.xlsx
+++ b/data/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jomaver/Library/CloudStorage/OneDrive-GrupoBancolombia/Otros/Trend_Digest/Riesgos/News-Scrapper/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86461C54-4E69-6645-90A4-036A889ED3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65EC631-0595-884F-B369-F04E3ECC6734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5540" yWindow="760" windowWidth="29020" windowHeight="15820" xr2:uid="{B4160771-E885-4268-9E3B-923D2C6334DB}"/>
   </bookViews>
@@ -65,110 +65,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="188">
   <si>
     <t>Emisor</t>
   </si>
   <si>
-    <t>ULTRACEM</t>
-  </si>
-  <si>
-    <t>UNE EPM</t>
-  </si>
-  <si>
-    <t>CONCONCRETO</t>
-  </si>
-  <si>
-    <t>CANACOL</t>
-  </si>
-  <si>
-    <t>EXCELCREDIT</t>
-  </si>
-  <si>
-    <t>DAVIVIENDA</t>
-  </si>
-  <si>
-    <t>Banco de Bogotá</t>
-  </si>
-  <si>
     <t>BBVA</t>
   </si>
   <si>
-    <t>Findeter</t>
-  </si>
-  <si>
-    <t>Banco Popular</t>
-  </si>
-  <si>
-    <t>Bancolombia</t>
-  </si>
-  <si>
-    <t>GNB Sudameris</t>
-  </si>
-  <si>
     <t>GRUPO ARGOS</t>
   </si>
   <si>
-    <t>Grupo SURA</t>
-  </si>
-  <si>
-    <t>PROMIGAS</t>
-  </si>
-  <si>
     <t>ECOPETROL</t>
   </si>
   <si>
-    <t>CEMENTOS ARGOS</t>
-  </si>
-  <si>
-    <t>INTERCONEXION ELECTRICA</t>
-  </si>
-  <si>
-    <t>ISA</t>
-  </si>
-  <si>
-    <t>CELSIA</t>
-  </si>
-  <si>
-    <t>MINEROS</t>
-  </si>
-  <si>
-    <t>EMPRESA DE ENERGIA DE BOGOTA</t>
-  </si>
-  <si>
-    <t>Banco de Occidente</t>
-  </si>
-  <si>
-    <t>Banco de la República</t>
-  </si>
-  <si>
-    <t>Corficolombiana</t>
-  </si>
-  <si>
-    <t>Scotiabank Colpatria</t>
-  </si>
-  <si>
-    <t>Colpatria</t>
-  </si>
-  <si>
-    <t>Banco AV Villas</t>
-  </si>
-  <si>
-    <t>FDN</t>
-  </si>
-  <si>
-    <t>Banco Santander</t>
-  </si>
-  <si>
-    <t>Bancoldex</t>
-  </si>
-  <si>
-    <t>Grupo Energía de Bogotá</t>
-  </si>
-  <si>
-    <t>ENEL</t>
-  </si>
-  <si>
     <t>Domain</t>
   </si>
   <si>
@@ -176,13 +86,556 @@
   </si>
   <si>
     <t>Lenguaje</t>
+  </si>
+  <si>
+    <t>CARVAJAL EMPAQUES S.A.</t>
+  </si>
+  <si>
+    <t>VALORES SIMESA S.A.</t>
+  </si>
+  <si>
+    <t>VALORES INDUSTRIALES SA</t>
+  </si>
+  <si>
+    <t>UNOSAN SA</t>
+  </si>
+  <si>
+    <t>UNE EPM TELECOMUNICACIONES SA</t>
+  </si>
+  <si>
+    <t>ULTRACEM S A S</t>
+  </si>
+  <si>
+    <t>TITULARIZADORA COLOMBIANA SA HITOS</t>
+  </si>
+  <si>
+    <t>TERMOCAUCA SA E S P EN LIQUIDACION</t>
+  </si>
+  <si>
+    <t>SURAMERICANA SA</t>
+  </si>
+  <si>
+    <t>SODIMAC COLOMBIA SA</t>
+  </si>
+  <si>
+    <t>SOCIEDAD PORTAFOLIO S A</t>
+  </si>
+  <si>
+    <t>SETAS COLOMBIANAS SA SETAS SA</t>
+  </si>
+  <si>
+    <t>SCOTIABANK COLPATRIA SA</t>
+  </si>
+  <si>
+    <t>RIOPAILA CASTILLA SA</t>
+  </si>
+  <si>
+    <t>RIOPAILA AGRICOLA SA</t>
+  </si>
+  <si>
+    <t>RENTA ALTERNATIVO GLOBAL</t>
+  </si>
+  <si>
+    <t>RCI COLOMBIA SA CF</t>
+  </si>
+  <si>
+    <t>PROTECCION SA</t>
+  </si>
+  <si>
+    <t>PROMIORIENTE SA ESP</t>
+  </si>
+  <si>
+    <t>PROMIGAS SA ESP</t>
+  </si>
+  <si>
+    <t>PRODUCTOS FAMILIA SA</t>
+  </si>
+  <si>
+    <t>PRIMAX COLOMBIA SA</t>
+  </si>
+  <si>
+    <t>ORGANIZACION TERPEL SA</t>
+  </si>
+  <si>
+    <t>ODINSA SA</t>
+  </si>
+  <si>
+    <t>MINISTERIO DE HACIENDA Y CREDITO PUBLICO</t>
+  </si>
+  <si>
+    <t>MINISTERIO DE CULTURA</t>
+  </si>
+  <si>
+    <t>MINEROS SA</t>
+  </si>
+  <si>
+    <t>MAYAGUEZ SA</t>
+  </si>
+  <si>
+    <t>MANUFACTURAS DE CEMENTO S A - EN REORGANIZACION</t>
+  </si>
+  <si>
+    <t>LA HIPOTECARIA COMPAÑIA DE FINANCIAMIENTO SA</t>
+  </si>
+  <si>
+    <t>KARTAL SA</t>
+  </si>
+  <si>
+    <t>ITAU COLOMBIA SA</t>
+  </si>
+  <si>
+    <t>ISAGEN SA ESP</t>
+  </si>
+  <si>
+    <t>INVERSIONES EQUIPOS Y SERVICIOS S.A.</t>
+  </si>
+  <si>
+    <t>INVERSIONES VENECIA S A INVENSA S A</t>
+  </si>
+  <si>
+    <t>INTERCONEXION ELECTRICA SA ESP</t>
+  </si>
+  <si>
+    <t>INSTITUTO COLOMBIANO DE CREDITO EDUCATIVO ICETEX</t>
+  </si>
+  <si>
+    <t>INDUSTRIAS ESTRA SA</t>
+  </si>
+  <si>
+    <t>GRUPO NUTRESA SA</t>
+  </si>
+  <si>
+    <t>GRUPO IMSA SA</t>
+  </si>
+  <si>
+    <t>GRUPO ENERGIA BOGOTA SA ESP</t>
+  </si>
+  <si>
+    <t>GRUPO DE INVERSIONES SURAMERICANA SA</t>
+  </si>
+  <si>
+    <t>GRUPO BOLIVAR SA</t>
+  </si>
+  <si>
+    <t>GRUPO AVAL ACCIONES Y VALORES SA</t>
+  </si>
+  <si>
+    <t>GRUPO ARGOS SA</t>
+  </si>
+  <si>
+    <t>GROUPE SEB ANDEAN SA</t>
+  </si>
+  <si>
+    <t>GM FINANCIAL COLOMBIA SA CIA DE FINANCIAMIENTO</t>
+  </si>
+  <si>
+    <t>GASES DE OCCIDENTE SA ESP</t>
+  </si>
+  <si>
+    <t>GAS NATURAL DEL ORIENTE SA ESP</t>
+  </si>
+  <si>
+    <t>FONDO GANADERO DE CUNDINAMARCA S A</t>
+  </si>
+  <si>
+    <t>FONDO DE INVERSION COLECTIVA INMOBILIARIO INMOVAL</t>
+  </si>
+  <si>
+    <t>FONDO DE INVERSION COLECTIVA ABIERTA RENTA FIJA PL</t>
+  </si>
+  <si>
+    <t>FONDO BURSATIL ISHARES COLCAP</t>
+  </si>
+  <si>
+    <t>FONDO BURSATIL HORIZONS COLOMBIA SELECT DE SYP</t>
+  </si>
+  <si>
+    <t>FONDO BUFALERO DEL CENTRO S A</t>
+  </si>
+  <si>
+    <t>FONDO ABIERTO POR COMPARTIMIENTOS VALORE</t>
+  </si>
+  <si>
+    <t>FINANZAUTO SA</t>
+  </si>
+  <si>
+    <t>FINANCIERA JURISCOOP SA COMPAÑIA DE FINANCIAMIENTO</t>
+  </si>
+  <si>
+    <t>FINANCIERA DE DESARROLLO TERRITORIAL SA FINDETER</t>
+  </si>
+  <si>
+    <t>FINANCIERA DE DESARROLLO NACIONAL SA</t>
+  </si>
+  <si>
+    <t>FIDUCIARIA COLMENA FIDEICOMISOS</t>
+  </si>
+  <si>
+    <t>FIC INMOBILIARIO SURA AM RENTAS INMOBILIARIAS</t>
+  </si>
+  <si>
+    <t>FIC ABIERTO RENTA ALTA CONVICCION</t>
+  </si>
+  <si>
+    <t>FIC ABIERTO FIDUCUENTA</t>
+  </si>
+  <si>
+    <t>FCP PACTIA INMOBILIARIO</t>
+  </si>
+  <si>
+    <t>FCP CARTAMA COMPARTIMENTO II INVERPALTAS</t>
+  </si>
+  <si>
+    <t>FCP CARTAMA COMPARTIMENTO GLOBAL</t>
+  </si>
+  <si>
+    <t>FABRICATO S.A.</t>
+  </si>
+  <si>
+    <t>EXCELCREDIT SA</t>
+  </si>
+  <si>
+    <t>EVERFIT SA</t>
+  </si>
+  <si>
+    <t>ETERNIT COLOMBIANA SA</t>
+  </si>
+  <si>
+    <t>ESTRATEGIAS ALTERNATIVAS</t>
+  </si>
+  <si>
+    <t>ENKA DE COLOMBIA SA</t>
+  </si>
+  <si>
+    <t>ENEL COLOMBIA SA ESP</t>
+  </si>
+  <si>
+    <t>EMPRESAS PUBLICAS DE MEDELLIN E.S.P.</t>
+  </si>
+  <si>
+    <t>EMPRESA DE TELECOMUNICACIONES DE BOGOTA SA ESP</t>
+  </si>
+  <si>
+    <t>EDITORIAL EL GLOBO SA EN LIQUIDACION</t>
+  </si>
+  <si>
+    <t>ECOPETROL SA</t>
+  </si>
+  <si>
+    <t>DEXCO COLOMBIA S.A.</t>
+  </si>
+  <si>
+    <t>CREDIVALORES CREDISERVICIOS SA</t>
+  </si>
+  <si>
+    <t>CORPORACION FINANCIERA COLOMBIANA SA</t>
+  </si>
+  <si>
+    <t>CORPORACION DE FERIAS Y EXPOSICIONES CORFERIAS SA</t>
+  </si>
+  <si>
+    <t>COOMEVA ENTIDAD PROMOTORA DE SALUD SA</t>
+  </si>
+  <si>
+    <t>CONSTRUCTORA CONCONCRETO SA</t>
+  </si>
+  <si>
+    <t>CONSTRUCCIONES EL CONDOR SA</t>
+  </si>
+  <si>
+    <t>COMPAÑIA DE MEDICINA PREPAGADA COLSANITAS S A</t>
+  </si>
+  <si>
+    <t>COMPAÑIA AGRICOLA SAN FELIPE S A</t>
+  </si>
+  <si>
+    <t>COMPANIA DE EMPAQUES SA</t>
+  </si>
+  <si>
+    <t>COLTEJER SA</t>
+  </si>
+  <si>
+    <t>COLTEFINANCIERA SA COMPAÑIA DE FINANCIAMIENTO</t>
+  </si>
+  <si>
+    <t>COLOMBINA SA</t>
+  </si>
+  <si>
+    <t>COLOMBIA TELECOMUNICACIONES S.A E.S.P BIC</t>
+  </si>
+  <si>
+    <t>CLINICA DE MARLY SA</t>
+  </si>
+  <si>
+    <t>CIA DE FINANCIAMIENTO TUYA SA</t>
+  </si>
+  <si>
+    <t>CIA DE ELECTRICIDAD DE TULUA SA ESP</t>
+  </si>
+  <si>
+    <t>CEMEX COLOMBIA SA</t>
+  </si>
+  <si>
+    <t>CEMENTOS ARGOS S.A</t>
+  </si>
+  <si>
+    <t>CELSIA SA</t>
+  </si>
+  <si>
+    <t>CELSIA COLOMBIA SA ESP</t>
+  </si>
+  <si>
+    <t>CASTILLA AGRICOLA SA</t>
+  </si>
+  <si>
+    <t>CARVAJAL SA</t>
+  </si>
+  <si>
+    <t>CARTON DE COLOMBIA SA</t>
+  </si>
+  <si>
+    <t>CARTERA COLECTIVA ABIERTA RENTA LIQUIDEZ VALORES B</t>
+  </si>
+  <si>
+    <t>BOLSA DE VALORES DE COLOMBIA SA</t>
+  </si>
+  <si>
+    <t>BOGOTA DISTRITO CAPITAL</t>
+  </si>
+  <si>
+    <t>BMC BOLSA MERCANTIL DE COLOMBIA SA</t>
+  </si>
+  <si>
+    <t>BAVARIA &amp; CIA S C A</t>
+  </si>
+  <si>
+    <t>BANCOLOMBIA SA</t>
+  </si>
+  <si>
+    <t>BANCO W SA</t>
+  </si>
+  <si>
+    <t>BANCO SERFINANZA SA</t>
+  </si>
+  <si>
+    <t>BANCO SANTANDER DE NEGOCIOS COLOMBIA SA</t>
+  </si>
+  <si>
+    <t>BANCO POPULAR SA</t>
+  </si>
+  <si>
+    <t>BANCO PICHINCHA SA</t>
+  </si>
+  <si>
+    <t>BANCO MUNDO MUJER</t>
+  </si>
+  <si>
+    <t>BANCO J.P. MORGAN COLOMBIA S.A.</t>
+  </si>
+  <si>
+    <t>BANCO GNB SUDAMERIS SA</t>
+  </si>
+  <si>
+    <t>BANCO FINANDINA SA FINANDINA ESTABLECIMIENTO BANCA</t>
+  </si>
+  <si>
+    <t>BANCO FALABELLA SA</t>
+  </si>
+  <si>
+    <t>BANCO DE OCCIDENTE</t>
+  </si>
+  <si>
+    <t>BANCO DE LA REPUBLICA</t>
+  </si>
+  <si>
+    <t>BANCO DE COMERCIO EXTERIOR DE COLOMBIA SA</t>
+  </si>
+  <si>
+    <t>BANCO DE BOGOTA SA</t>
+  </si>
+  <si>
+    <t>BANCO DAVIVIENDA SA</t>
+  </si>
+  <si>
+    <t>BANCO COMERCIAL AV VILLAS SA</t>
+  </si>
+  <si>
+    <t>BANCO CAJA SOCIAL SA</t>
+  </si>
+  <si>
+    <t>BANCO BTG PACTUAL COLOMBIA S.A</t>
+  </si>
+  <si>
+    <t>BANCO BBVA COLOMBIA SA</t>
+  </si>
+  <si>
+    <t>BANCO AGRARIO DE COLOMBIA SA</t>
+  </si>
+  <si>
+    <t>BANCIEN S.A Y/O BAN100 S.A</t>
+  </si>
+  <si>
+    <t>AZUL &amp; BLANCO MILLONARIOS F C SA</t>
+  </si>
+  <si>
+    <t>ALMACENES EXITO SA</t>
+  </si>
+  <si>
+    <t>AGROGUACHAL</t>
+  </si>
+  <si>
+    <t>ACERIAS PAZ DEL RIO SA</t>
+  </si>
+  <si>
+    <t>BAC Holding</t>
+  </si>
+  <si>
+    <t>TITULARIZADORA COLOMBIANA</t>
+  </si>
+  <si>
+    <t>BANCO PICHINCHA</t>
+  </si>
+  <si>
+    <t>RINKER MATERIALS</t>
+  </si>
+  <si>
+    <t>BLADEX</t>
+  </si>
+  <si>
+    <t>BANCO LATINOAMERICANO DE COMERCIO EXTERIOR</t>
+  </si>
+  <si>
+    <t>HUNT OIL</t>
+  </si>
+  <si>
+    <t>CHARTER COMMUNICATIONS</t>
+  </si>
+  <si>
+    <t>MERCADOLIBRE</t>
+  </si>
+  <si>
+    <t>SANTANDER HLDGS</t>
+  </si>
+  <si>
+    <t>INVESTMENT ENERGY</t>
+  </si>
+  <si>
+    <t>BOEING</t>
+  </si>
+  <si>
+    <t>GLOBAL BANK</t>
+  </si>
+  <si>
+    <t>BANCO BTG PACTUAL</t>
+  </si>
+  <si>
+    <t>BANISTMO SA</t>
+  </si>
+  <si>
+    <t>PRIMAX</t>
+  </si>
+  <si>
+    <t>ULTRACEM S.A.S</t>
+  </si>
+  <si>
+    <t>Isagen</t>
+  </si>
+  <si>
+    <t>ICETEX</t>
+  </si>
+  <si>
+    <t>BANCO DE LAS MICROFINANZAS BANCAMIA</t>
+  </si>
+  <si>
+    <t>ORGANIZACION TERPEL</t>
+  </si>
+  <si>
+    <t>BANCO FINANDINA</t>
+  </si>
+  <si>
+    <t>BANCO SERFINANZA</t>
+  </si>
+  <si>
+    <t>BANCO AGRARIO</t>
+  </si>
+  <si>
+    <t>BANCO CAJA SOCIAL</t>
+  </si>
+  <si>
+    <t>ITAU CORPBANCA</t>
+  </si>
+  <si>
+    <t>BANCO COMERCIAL AV VILLAS</t>
+  </si>
+  <si>
+    <t>BNP PARIBAS</t>
+  </si>
+  <si>
+    <t>Banco GNB Sudameris</t>
+  </si>
+  <si>
+    <t>BANCO SANTANDER</t>
+  </si>
+  <si>
+    <t>BANCO SANTANDER DE NEGOCIOS COLOMBIA</t>
+  </si>
+  <si>
+    <t>CITIBANK</t>
+  </si>
+  <si>
+    <t>SOCIEDADES BOLIVAR</t>
+  </si>
+  <si>
+    <t>FINANCIERA DE DESARROLLO NACIONAL</t>
+  </si>
+  <si>
+    <t>CARVAJAL</t>
+  </si>
+  <si>
+    <t>SCOTIABANK</t>
+  </si>
+  <si>
+    <t>SCOTIABANK COLPATRIA S.A</t>
+  </si>
+  <si>
+    <t>BANCOLDEX</t>
+  </si>
+  <si>
+    <t>BANCO DE COMERCIO EXTERIOR DE COLOMBIA</t>
+  </si>
+  <si>
+    <t>SURAMERICANA</t>
+  </si>
+  <si>
+    <t>EPM</t>
+  </si>
+  <si>
+    <t>EMPRESAS PUBLICAS DE MEDELLIN</t>
+  </si>
+  <si>
+    <t>FINANCIERA DE DESARROLLO TERRITORIAL</t>
+  </si>
+  <si>
+    <t>FINDETER</t>
+  </si>
+  <si>
+    <t>BANCO BBVA</t>
+  </si>
+  <si>
+    <t>Davivienda</t>
+  </si>
+  <si>
+    <t>Grupo Nutresa</t>
+  </si>
+  <si>
+    <t>Cementos Argos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -198,6 +651,12 @@
     <font>
       <b/>
       <sz val="12"/>
+      <name val="CIBFont Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="CIBFont Sans"/>
       <family val="2"/>
     </font>
@@ -243,16 +702,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -587,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B14AF44F-A1D1-414E-897F-ECD542EC8E25}">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B192"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="42.1640625" style="1" customWidth="1"/>
@@ -600,172 +1056,962 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>2</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>4</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
-        <v>5</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="4" t="s">
-        <v>6</v>
+      <c r="A7" s="3" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="4" t="s">
-        <v>7</v>
+      <c r="A8" s="3" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="4" t="s">
-        <v>8</v>
+      <c r="A9" s="3" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="4" t="s">
-        <v>9</v>
+      <c r="A10" s="3" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="4" t="s">
-        <v>10</v>
+      <c r="A11" s="3" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="4" t="s">
-        <v>11</v>
+      <c r="A12" s="3" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="4" t="s">
-        <v>12</v>
+      <c r="A13" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3" t="s">
-        <v>13</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>14</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>15</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="3" t="s">
-        <v>16</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="3" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="3" t="s">
-        <v>19</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="3" t="s">
-        <v>20</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="3" t="s">
-        <v>21</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="4" t="s">
-        <v>33</v>
+    <row r="178" spans="1:1">
+      <c r="A178" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -780,12 +2026,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
